--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-09-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_30-09-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -780,37 +780,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£15.25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£15.25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£17.50-Sale Price old price: £21.95</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>£15.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>£15.30</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>£15.30</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£17.50-Sale Price old price: £21.95</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£15.38</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>£15.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.45</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.45</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.45</t>
+          <t>£15.50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.95</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1385,42 +1385,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£25.15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£25.15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£25.15</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>£29.00-Sale Price old price: £34.95</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>£25.26</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>£25.18</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>£25.18</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£25.18</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£29.00-Sale Price old price: £34.95</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>£25.26</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>£25.18</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>£35.35 presale price: £52.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1506,37 +1506,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£27.25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£27.25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£27.25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£32.00-Sale Price old price: £35.95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>£27.33</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>£27.27</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£27.27</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£27.27</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£32.00-Sale Price old price: £35.95</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£27.33</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£27.30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.82</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.92</t>
+          <t>£32.89</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.92</t>
+          <t>£32.89</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.92</t>
+          <t>£32.89</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.18</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.18</t>
+          <t>£40.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£40.89</t>
+          <t>£40.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.89</t>
+          <t>£40.85</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.89</t>
+          <t>£40.85</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff71b361eb5+80197]
-	GetHandleVerifier [0x0x7ff71b361f10+80288]
-	(No symbol) [0x0x7ff71b0e02fa]
-	(No symbol) [0x0x7ff71b137cd7]
-	(No symbol) [0x0x7ff71b137f9c]
-	(No symbol) [0x0x7ff71b18ba87]
-	(No symbol) [0x0x7ff71b1603bf]
-	(No symbol) [0x0x7ff71b1887fb]
-	(No symbol) [0x0x7ff71b160153]
-	(No symbol) [0x0x7ff71b128b02]
-	(No symbol) [0x0x7ff71b1298d3]
-	GetHandleVerifier [0x0x7ff71b61e83d+2949837]
-	GetHandleVerifier [0x0x7ff71b618c6a+2926330]
-	GetHandleVerifier [0x0x7ff71b6386c7+3055959]
-	GetHandleVerifier [0x0x7ff71b37cfee+191102]
-	GetHandleVerifier [0x0x7ff71b3850af+224063]
-	GetHandleVerifier [0x0x7ff71b36af64+117236]
-	GetHandleVerifier [0x0x7ff71b36b119+117673]
-	GetHandleVerifier [0x0x7ff71b3510a8+11064]
-	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
-	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+	GetHandleVerifier [0x0x7ff79e041eb5+80197]
+	GetHandleVerifier [0x0x7ff79e041f10+80288]
+	(No symbol) [0x0x7ff79ddc02fa]
+	(No symbol) [0x0x7ff79de17cd7]
+	(No symbol) [0x0x7ff79de17f9c]
+	(No symbol) [0x0x7ff79de6ba87]
+	(No symbol) [0x0x7ff79de403bf]
+	(No symbol) [0x0x7ff79de687fb]
+	(No symbol) [0x0x7ff79de40153]
+	(No symbol) [0x0x7ff79de08b02]
+	(No symbol) [0x0x7ff79de098d3]
+	GetHandleVerifier [0x0x7ff79e2fe83d+2949837]
+	GetHandleVerifier [0x0x7ff79e2f8c6a+2926330]
+	GetHandleVerifier [0x0x7ff79e3186c7+3055959]
+	GetHandleVerifier [0x0x7ff79e05cfee+191102]
+	GetHandleVerifier [0x0x7ff79e0650af+224063]
+	GetHandleVerifier [0x0x7ff79e04af64+117236]
+	GetHandleVerifier [0x0x7ff79e04b119+117673]
+	GetHandleVerifier [0x0x7ff79e0310a8+11064]
+	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
+	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
         </is>
       </c>
